--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137294691</v>
       </c>
       <c r="B2" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,52 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137294688</v>
+        <v>137329995</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>92122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754757</v>
+        <v>754792</v>
       </c>
       <c r="R3" t="n">
-        <v>7174606</v>
+        <v>7174563</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,69 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294688</t>
+          <t>https://artportalen.se/Sighting/137329995</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137294689</v>
+        <v>137329996</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754815</v>
+        <v>754786</v>
       </c>
       <c r="R4" t="n">
-        <v>7174609</v>
+        <v>7174560</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,69 +999,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294689</t>
+          <t>https://artportalen.se/Sighting/137329996</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137294690</v>
+        <v>137329993</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754674</v>
+        <v>754726</v>
       </c>
       <c r="R5" t="n">
-        <v>7174615</v>
+        <v>7174597</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,18 +1111,834 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137329993</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137329994</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79513</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>754798</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7174569</v>
+      </c>
+      <c r="S6" t="n">
+        <v>19</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137329997</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79513</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>754810</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7174602</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329997</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137329998</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79513</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>754768</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174623</v>
+      </c>
+      <c r="S8" t="n">
+        <v>16</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329998</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137294688</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>754757</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7174606</v>
+      </c>
+      <c r="S9" t="n">
+        <v>16</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294688</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137294689</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>754815</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7174609</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294689</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137294690</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>754674</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7174615</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137294690</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137329999</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>754724</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7174627</v>
+      </c>
+      <c r="S12" t="n">
+        <v>28</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329999</t>
         </is>
       </c>
     </row>
@@ -1159,6 +1948,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137294691</v>
+        <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754674</v>
+        <v>754780</v>
       </c>
       <c r="R2" t="n">
-        <v>7174599</v>
+        <v>7174565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,92 +755,90 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294691</t>
+          <t>https://artportalen.se/Sighting/137362831</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137329995</v>
+        <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>92176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754792</v>
+        <v>754700</v>
       </c>
       <c r="R3" t="n">
-        <v>7174563</v>
+        <v>7174614</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +865,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:33</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på undersidan av en mycket gammal tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,71 +881,79 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329995</t>
+          <t>https://artportalen.se/Sighting/137362951</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137329996</v>
+        <v>137362859</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754786</v>
+        <v>754781</v>
       </c>
       <c r="R4" t="n">
-        <v>7174560</v>
+        <v>7174568</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,76 +980,67 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329996</t>
+          <t>https://artportalen.se/Sighting/137362859</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137329993</v>
+        <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754726</v>
+        <v>754674</v>
       </c>
       <c r="R5" t="n">
-        <v>7174597</v>
+        <v>7174599</v>
       </c>
       <c r="S5" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,49 +1110,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329993</t>
+          <t>https://artportalen.se/Sighting/137294691</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137329994</v>
+        <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754798</v>
+        <v>754792</v>
       </c>
       <c r="R6" t="n">
-        <v>7174569</v>
+        <v>7174563</v>
       </c>
       <c r="S6" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,38 +1233,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329994</t>
+          <t>https://artportalen.se/Sighting/137329995</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137329997</v>
+        <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754810</v>
+        <v>754786</v>
       </c>
       <c r="R7" t="n">
-        <v>7174602</v>
+        <v>7174560</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1345,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329997</t>
+          <t>https://artportalen.se/Sighting/137329996</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137329998</v>
+        <v>137329993</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754768</v>
+        <v>754726</v>
       </c>
       <c r="R8" t="n">
-        <v>7174623</v>
+        <v>7174597</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,58 +1457,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329998</t>
+          <t>https://artportalen.se/Sighting/137329993</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137294688</v>
+        <v>137329994</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754757</v>
+        <v>754798</v>
       </c>
       <c r="R9" t="n">
-        <v>7174606</v>
+        <v>7174569</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1543,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,69 +1558,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294688</t>
+          <t>https://artportalen.se/Sighting/137329994</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137294689</v>
+        <v>137329997</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754815</v>
+        <v>754810</v>
       </c>
       <c r="R10" t="n">
-        <v>7174609</v>
+        <v>7174602</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,69 +1670,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294689</t>
+          <t>https://artportalen.se/Sighting/137329997</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137294690</v>
+        <v>137329998</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754674</v>
+        <v>754768</v>
       </c>
       <c r="R11" t="n">
-        <v>7174615</v>
+        <v>7174623</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,12 +1767,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,65 +1782,72 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294690</t>
+          <t>https://artportalen.se/Sighting/137329998</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137329999</v>
+        <v>137362878</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Orrmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754724</v>
+        <v>754806</v>
       </c>
       <c r="R12" t="n">
-        <v>7174627</v>
+        <v>7174600</v>
       </c>
       <c r="S12" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,50 +1874,1185 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137362878</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137362899</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79516</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>754781</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7174634</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>fertil</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137362899</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137362932</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79516</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>754714</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7174641</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137362932</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137362846</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58031</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>754779</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7174569</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137362846</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137294688</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>754757</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7174606</v>
+      </c>
+      <c r="S16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294688</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137294689</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>754815</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7174609</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294689</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137294690</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>754674</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7174615</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294690</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137329999</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>754724</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7174627</v>
+      </c>
+      <c r="S19" t="n">
+        <v>28</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137329999</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137362892</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>754802</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7174609</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137362892</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137362906</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>754722</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7174630</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137362906</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137362959</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>754747</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7174582</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137362959</t>
         </is>
       </c>
     </row>
@@ -1955,6 +3069,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137362859</v>
       </c>
       <c r="B4" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329993</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137329994</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137329997</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>137329998</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>137362878</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137362899</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137362932</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137362846</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>137294688</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137294689</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137294690</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>137329999</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137362892</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>137362906</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137362959</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137362859</v>
       </c>
       <c r="B4" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329993</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137329994</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137329997</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>137329998</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>137362878</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137362899</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137362932</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137362859</v>
       </c>
       <c r="B4" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329993</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137329994</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137329997</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>137329998</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>137362878</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137362899</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137362932</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137362859</v>
       </c>
       <c r="B4" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329993</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137329994</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137329997</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>137329998</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>137362878</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137362899</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137362932</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44408-2025 artfynd.xlsx
+++ b/artfynd/A 44408-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137362831</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137362951</v>
       </c>
       <c r="B3" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137362859</v>
       </c>
       <c r="B4" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137294691</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329995</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329996</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329993</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137329994</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137329997</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>137329998</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>137362878</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137362899</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137362932</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137362846</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>137294688</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137294689</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137294690</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>137329999</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137362892</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>137362906</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137362959</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
